--- a/data/chart/input/old_chart_14/2024年中考数学分析数据存档.xlsx
+++ b/data/chart/input/old_chart_14/2024年中考数学分析数据存档.xlsx
@@ -3,14 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_02CEA2034204834BE2BD92100A7D89E9494ACDCD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BBD99D0-4764-4EDF-9FAF-FD49127FA914}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_02CEA2034204834BE2BD92100A7D89E9494ACDCD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF74353D-E46B-4D41-9A23-12D3B054D391}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="15">
   <si>
     <t>年份</t>
   </si>
@@ -78,24 +77,6 @@
   </si>
   <si>
     <t>数学与人文艺术的融合</t>
-  </si>
-  <si>
-    <t>内在可分离型</t>
-  </si>
-  <si>
-    <t>陈杨</t>
-  </si>
-  <si>
-    <t>内在不可分离型</t>
-  </si>
-  <si>
-    <t>姚桂香</t>
-  </si>
-  <si>
-    <t>鞠艳</t>
-  </si>
-  <si>
-    <t>娄琴</t>
   </si>
 </sst>
 </file>
@@ -641,157 +622,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -799,15 +629,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -955,14 +776,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F7033F-00D0-4FCD-920D-6A168412AD5F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E0874EA-60E0-45CF-AF1B-A43F96E80A60}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D99B2BFD-B82E-4A75-8221-C1D8DD8EE686}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E0874EA-60E0-45CF-AF1B-A43F96E80A60}"/>
 </file>